--- a/tame_output/ON/bt/strategyON_20240102.xlsx
+++ b/tame_output/ON/bt/strategyON_20240102.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>486.7%</t>
+          <t>486.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>103.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
     </row>
@@ -43641,16 +43641,16 @@
         <v>3.125814472478857</v>
       </c>
       <c r="D1830" t="n">
-        <v>-0.01086593413527559</v>
+        <v>-0.01227023237236546</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.121111674510999</v>
+        <v>3.120549955216164</v>
       </c>
       <c r="F1830" t="n">
-        <v>1.629545432689424</v>
+        <v>1.628141134452334</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.103541732092513</v>
+        <v>4.102699153150259</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240102.xlsx
+++ b/tame_output/ON/bt/strategyON_20240102.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>486.6%</t>
+          <t>486.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -43641,16 +43641,16 @@
         <v>3.125814472478857</v>
       </c>
       <c r="D1830" t="n">
-        <v>-0.01227023237236546</v>
+        <v>-0.01288552124429998</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.120549955216164</v>
+        <v>3.12030383966739</v>
       </c>
       <c r="F1830" t="n">
-        <v>1.628141134452334</v>
+        <v>1.6275258455804</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.102699153150259</v>
+        <v>4.102329979827098</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240102.xlsx
+++ b/tame_output/ON/bt/strategyON_20240102.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>486.5%</t>
+          <t>475.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>105.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>100.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -43641,16 +43641,16 @@
         <v>3.125814472478857</v>
       </c>
       <c r="D1830" t="n">
-        <v>-0.01288552124429998</v>
+        <v>-0.1160746335925767</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.12030383966739</v>
+        <v>3.079028194728079</v>
       </c>
       <c r="F1830" t="n">
-        <v>1.6275258455804</v>
+        <v>1.524336733232123</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.102329979827098</v>
+        <v>4.040416512418132</v>
       </c>
     </row>
   </sheetData>
